--- a/astro-site/public/dl/pack-appcc/08-matriz-alergenos.xlsx
+++ b/astro-site/public/dl/pack-appcc/08-matriz-alergenos.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Matriz Alérgenos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Alérgenos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Matriz Alérgenos'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -126,42 +128,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -521,15 +523,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -537,6 +540,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -544,9 +548,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -582,9 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -592,9 +592,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -623,13 +621,19 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -637,7 +641,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -646,28 +659,28 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="8"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="15"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
-    <col customWidth="1" max="8" min="8" width="12"/>
-    <col customWidth="1" max="9" min="9" width="12"/>
-    <col customWidth="1" max="10" min="10" width="12"/>
-    <col customWidth="1" max="11" min="11" width="12"/>
-    <col customWidth="1" max="12" min="12" width="12"/>
-    <col customWidth="1" max="13" min="13" width="12"/>
-    <col customWidth="1" max="14" min="14" width="12"/>
-    <col customWidth="1" max="15" min="15" width="12"/>
-    <col customWidth="1" max="16" min="16" width="12"/>
-    <col customWidth="1" max="17" min="17" width="12"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +704,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -1618,6 +1632,7 @@
       <c r="P45" s="12" t="n"/>
       <c r="Q45" s="12" t="n"/>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" s="13" t="inlineStr">
         <is>
@@ -1626,61 +1641,62 @@
       </c>
       <c r="D47" s="14">
         <f>COUNTIF(D6:D45,"S")+COUNTIF(D6:D45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E47" s="14">
         <f>COUNTIF(E6:E45,"S")+COUNTIF(E6:E45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F47" s="14">
         <f>COUNTIF(F6:F45,"S")+COUNTIF(F6:F45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G47" s="14">
         <f>COUNTIF(G6:G45,"S")+COUNTIF(G6:G45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H47" s="14">
         <f>COUNTIF(H6:H45,"S")+COUNTIF(H6:H45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I47" s="14">
         <f>COUNTIF(I6:I45,"S")+COUNTIF(I6:I45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="J47" s="14">
         <f>COUNTIF(J6:J45,"S")+COUNTIF(J6:J45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="K47" s="14">
         <f>COUNTIF(K6:K45,"S")+COUNTIF(K6:K45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="L47" s="14">
         <f>COUNTIF(L6:L45,"S")+COUNTIF(L6:L45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="M47" s="14">
         <f>COUNTIF(M6:M45,"S")+COUNTIF(M6:M45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="N47" s="14">
         <f>COUNTIF(N6:N45,"S")+COUNTIF(N6:N45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="O47" s="14">
         <f>COUNTIF(O6:O45,"S")+COUNTIF(O6:O45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="P47" s="14">
         <f>COUNTIF(P6:P45,"S")+COUNTIF(P6:P45,"T")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="Q47" s="14">
         <f>COUNTIF(Q6:Q45,"S")+COUNTIF(Q6:Q45,"T")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
@@ -1707,14 +1723,22 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45" type="list">
+    <dataValidation sqref="D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,T,N"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45" type="list">
+    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Entrantes,Primeros,Segundos,Postres,Bebidas,Tapas,Desayunos,Infantil,Otros"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/08-matriz-alergenos.xlsx
+++ b/astro-site/public/dl/pack-appcc/08-matriz-alergenos.xlsx
@@ -6678,11 +6678,11 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A210:S210"/>
+    <mergeCell ref="A213:S213"/>
     <mergeCell ref="A211:S211"/>
     <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A213:S213"/>
+    <mergeCell ref="A212:S212"/>
     <mergeCell ref="A4:S4"/>
-    <mergeCell ref="A212:S212"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A214:S214"/>
   </mergeCells>
